--- a/v7_final_10020/analysis/unmatched_audit/review_sheet_v7.xlsx
+++ b/v7_final_10020/analysis/unmatched_audit/review_sheet_v7.xlsx
@@ -16,9 +16,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="집계" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'광고'!$A$1:$J$201</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'미디어'!$A$1:$J$201</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'지역'!$A$1:$J$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'광고'!$A$1:$K$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'미디어'!$A$1:$K$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'지역'!$A$1:$K$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -515,7 +515,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>A 누락·사전추가 — 이 지표에 잡혔어야 하고, 열 I '추가할 표현'에 적은 말을 사전에 넣으면 잡힌다. 예: '런닝맨', 'brand ambassador'.</t>
+          <t>A 누락·사전추가 — 이 지표에 잡혔어야 하고, 열 I '추가할 표현'에 문장에 나온 말 그대로(예: Seoul, 런닝맨, brand ambassador)를 적고, 열 J '집계 대상'에 그 말이 셀 곳을 고른다. 지역은 시·도(Seoul → 서울, 봉화 → 경북), 미디어는 서브태그(런닝맨 → 예능). 광고는 신호 목록 하나라 집계 대상이 없다.</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J201"/>
+  <dimension ref="A1:K201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1108,8 +1108,9 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1155,10 +1156,15 @@
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>추가할 표현(A일 때)</t>
+          <t>추가할 표현(A일 때, 문장에 나온 말 그대로)</t>
         </is>
       </c>
       <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>집계 대상(A일 때: 지역=시·도, 미디어=서브태그)</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1192,7 +1198,12 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="6" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1222,7 +1233,12 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="6" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1252,7 +1268,12 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" s="6" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1282,7 +1303,12 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" s="6" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1312,7 +1338,12 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" s="6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1342,7 +1373,12 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1372,7 +1408,12 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" s="6" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1402,7 +1443,12 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" s="6" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1432,7 +1478,12 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" s="6" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1462,7 +1513,12 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" s="6" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1492,7 +1548,12 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" s="6" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1522,7 +1583,12 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" s="6" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1552,7 +1618,12 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" s="6" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1582,7 +1653,12 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" s="6" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1612,7 +1688,12 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" s="6" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1642,7 +1723,12 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" s="6" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1672,7 +1758,12 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" s="6" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1702,7 +1793,12 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" s="6" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1732,7 +1828,12 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" s="6" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1762,7 +1863,12 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" s="6" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1792,7 +1898,12 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="6" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1822,7 +1933,12 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" s="6" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1852,7 +1968,12 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" s="6" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1882,7 +2003,12 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" s="6" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1912,7 +2038,12 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" s="6" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1942,7 +2073,12 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" s="6" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1972,7 +2108,12 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" s="6" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2002,7 +2143,12 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" s="6" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2032,7 +2178,12 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" s="6" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2062,7 +2213,12 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" s="6" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2092,7 +2248,12 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" s="6" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2122,7 +2283,12 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" s="6" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2152,7 +2318,12 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" s="6" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2182,7 +2353,12 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" s="6" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2212,7 +2388,12 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" s="6" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2242,7 +2423,12 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" s="6" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2272,7 +2458,12 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" s="6" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2302,7 +2493,12 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" s="6" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -2336,7 +2532,12 @@
       </c>
       <c r="H40" s="7" t="inlineStr"/>
       <c r="I40" s="7" t="inlineStr"/>
-      <c r="J40" s="7" t="inlineStr"/>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2370,7 +2571,12 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" s="6" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2400,7 +2606,12 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" s="6" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2430,7 +2641,12 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" s="6" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2460,7 +2676,12 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" s="6" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2490,7 +2711,12 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" s="6" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2520,7 +2746,12 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" s="6" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2550,7 +2781,12 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" s="6" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2580,7 +2816,12 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" s="6" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2610,7 +2851,12 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" s="6" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2640,7 +2886,12 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" s="6" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2670,7 +2921,12 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" s="6" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2700,7 +2956,12 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" s="6" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2730,7 +2991,12 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" s="6" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2760,7 +3026,12 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" s="6" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2790,7 +3061,12 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" s="6" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2820,7 +3096,12 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" s="6" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2850,7 +3131,12 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" s="6" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2880,7 +3166,12 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" s="6" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2910,7 +3201,12 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" s="6" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2940,7 +3236,12 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" s="6" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2970,7 +3271,12 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" s="6" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3000,7 +3306,12 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" s="6" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3030,7 +3341,12 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" s="6" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3060,7 +3376,12 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" s="6" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3090,7 +3411,12 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" s="6" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3120,7 +3446,12 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" s="6" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3150,7 +3481,12 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" s="6" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3180,7 +3516,12 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" s="6" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3210,7 +3551,12 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" s="6" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3240,7 +3586,12 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" s="6" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3270,7 +3621,12 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" s="6" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3300,7 +3656,12 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" s="6" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3330,7 +3691,12 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" s="6" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3360,7 +3726,12 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" s="6" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3394,7 +3765,12 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" s="6" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3428,7 +3804,12 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" s="6" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3458,7 +3839,12 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" s="6" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3488,7 +3874,12 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" s="6" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3518,7 +3909,12 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" s="6" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3548,7 +3944,12 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" s="6" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -3578,7 +3979,12 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" s="6" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -3608,7 +4014,12 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" s="6" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3638,7 +4049,12 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" s="6" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3668,7 +4084,12 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" s="6" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3698,7 +4119,12 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" s="6" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3728,7 +4154,12 @@
       <c r="G86" t="inlineStr"/>
       <c r="H86" s="6" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -3758,7 +4189,12 @@
       <c r="G87" t="inlineStr"/>
       <c r="H87" s="6" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -3788,7 +4224,12 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" s="6" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -3818,7 +4259,12 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" s="6" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -3848,7 +4294,12 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" s="6" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -3878,7 +4329,12 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" s="6" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -3908,7 +4364,12 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" s="6" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -3938,7 +4399,12 @@
       <c r="G93" t="inlineStr"/>
       <c r="H93" s="6" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -3968,7 +4434,12 @@
       <c r="G94" t="inlineStr"/>
       <c r="H94" s="6" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -3998,7 +4469,12 @@
       <c r="G95" t="inlineStr"/>
       <c r="H95" s="6" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4028,7 +4504,12 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" s="6" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4058,7 +4539,12 @@
       <c r="G97" t="inlineStr"/>
       <c r="H97" s="6" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4088,7 +4574,12 @@
       <c r="G98" t="inlineStr"/>
       <c r="H98" s="6" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4118,7 +4609,12 @@
       <c r="G99" t="inlineStr"/>
       <c r="H99" s="6" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4148,7 +4644,12 @@
       <c r="G100" t="inlineStr"/>
       <c r="H100" s="6" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4178,7 +4679,12 @@
       <c r="G101" t="inlineStr"/>
       <c r="H101" s="6" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -4208,7 +4714,12 @@
       <c r="G102" t="inlineStr"/>
       <c r="H102" s="6" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -4238,7 +4749,12 @@
       <c r="G103" t="inlineStr"/>
       <c r="H103" s="6" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -4268,7 +4784,12 @@
       <c r="G104" t="inlineStr"/>
       <c r="H104" s="6" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -4298,7 +4819,12 @@
       <c r="G105" t="inlineStr"/>
       <c r="H105" s="6" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -4328,7 +4854,12 @@
       <c r="G106" t="inlineStr"/>
       <c r="H106" s="6" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n">
@@ -4362,7 +4893,12 @@
       </c>
       <c r="H107" s="7" t="inlineStr"/>
       <c r="I107" s="7" t="inlineStr"/>
-      <c r="J107" s="7" t="inlineStr"/>
+      <c r="J107" s="7" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K107" s="7" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -4392,7 +4928,12 @@
       <c r="G108" t="inlineStr"/>
       <c r="H108" s="6" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -4422,7 +4963,12 @@
       <c r="G109" t="inlineStr"/>
       <c r="H109" s="6" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -4452,7 +4998,12 @@
       <c r="G110" t="inlineStr"/>
       <c r="H110" s="6" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -4482,7 +5033,12 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" s="6" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -4512,7 +5068,12 @@
       <c r="G112" t="inlineStr"/>
       <c r="H112" s="6" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -4542,7 +5103,12 @@
       <c r="G113" t="inlineStr"/>
       <c r="H113" s="6" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -4572,7 +5138,12 @@
       <c r="G114" t="inlineStr"/>
       <c r="H114" s="6" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -4602,7 +5173,12 @@
       <c r="G115" t="inlineStr"/>
       <c r="H115" s="6" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -4632,7 +5208,12 @@
       <c r="G116" t="inlineStr"/>
       <c r="H116" s="6" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -4662,7 +5243,12 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" s="6" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -4692,7 +5278,12 @@
       <c r="G118" t="inlineStr"/>
       <c r="H118" s="6" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -4722,7 +5313,12 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" s="6" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -4752,7 +5348,12 @@
       <c r="G120" t="inlineStr"/>
       <c r="H120" s="6" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -4782,7 +5383,12 @@
       <c r="G121" t="inlineStr"/>
       <c r="H121" s="6" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -4812,7 +5418,12 @@
       <c r="G122" t="inlineStr"/>
       <c r="H122" s="6" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -4842,7 +5453,12 @@
       <c r="G123" t="inlineStr"/>
       <c r="H123" s="6" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -4872,7 +5488,12 @@
       <c r="G124" t="inlineStr"/>
       <c r="H124" s="6" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -4902,7 +5523,12 @@
       <c r="G125" t="inlineStr"/>
       <c r="H125" s="6" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -4932,7 +5558,12 @@
       <c r="G126" t="inlineStr"/>
       <c r="H126" s="6" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -4962,7 +5593,12 @@
       <c r="G127" t="inlineStr"/>
       <c r="H127" s="6" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -4992,7 +5628,12 @@
       <c r="G128" t="inlineStr"/>
       <c r="H128" s="6" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -5022,7 +5663,12 @@
       <c r="G129" t="inlineStr"/>
       <c r="H129" s="6" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -5052,7 +5698,12 @@
       <c r="G130" t="inlineStr"/>
       <c r="H130" s="6" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="7" t="n">
@@ -5086,7 +5737,12 @@
       </c>
       <c r="H131" s="7" t="inlineStr"/>
       <c r="I131" s="7" t="inlineStr"/>
-      <c r="J131" s="7" t="inlineStr"/>
+      <c r="J131" s="7" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K131" s="7" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -5116,7 +5772,12 @@
       <c r="G132" t="inlineStr"/>
       <c r="H132" s="6" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -5146,7 +5807,12 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" s="6" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -5176,7 +5842,12 @@
       <c r="G134" t="inlineStr"/>
       <c r="H134" s="6" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -5206,7 +5877,12 @@
       <c r="G135" t="inlineStr"/>
       <c r="H135" s="6" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -5236,7 +5912,12 @@
       <c r="G136" t="inlineStr"/>
       <c r="H136" s="6" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -5266,7 +5947,12 @@
       <c r="G137" t="inlineStr"/>
       <c r="H137" s="6" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -5296,7 +5982,12 @@
       <c r="G138" t="inlineStr"/>
       <c r="H138" s="6" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -5326,7 +6017,12 @@
       <c r="G139" t="inlineStr"/>
       <c r="H139" s="6" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -5356,7 +6052,12 @@
       <c r="G140" t="inlineStr"/>
       <c r="H140" s="6" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -5386,7 +6087,12 @@
       <c r="G141" t="inlineStr"/>
       <c r="H141" s="6" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -5416,7 +6122,12 @@
       <c r="G142" t="inlineStr"/>
       <c r="H142" s="6" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -5446,7 +6157,12 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" s="6" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -5476,7 +6192,12 @@
       <c r="G144" t="inlineStr"/>
       <c r="H144" s="6" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -5506,7 +6227,12 @@
       <c r="G145" t="inlineStr"/>
       <c r="H145" s="6" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -5536,7 +6262,12 @@
       <c r="G146" t="inlineStr"/>
       <c r="H146" s="6" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -5566,7 +6297,12 @@
       <c r="G147" t="inlineStr"/>
       <c r="H147" s="6" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -5596,7 +6332,12 @@
       <c r="G148" t="inlineStr"/>
       <c r="H148" s="6" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -5626,7 +6367,12 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" s="6" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -5656,7 +6402,12 @@
       <c r="G150" t="inlineStr"/>
       <c r="H150" s="6" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -5686,7 +6437,12 @@
       <c r="G151" t="inlineStr"/>
       <c r="H151" s="6" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -5716,7 +6472,12 @@
       <c r="G152" t="inlineStr"/>
       <c r="H152" s="6" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -5746,7 +6507,12 @@
       <c r="G153" t="inlineStr"/>
       <c r="H153" s="6" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -5776,7 +6542,12 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" s="6" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -5806,7 +6577,12 @@
       <c r="G155" t="inlineStr"/>
       <c r="H155" s="6" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -5836,7 +6612,12 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" s="6" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -5866,7 +6647,12 @@
       <c r="G157" t="inlineStr"/>
       <c r="H157" s="6" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -5896,7 +6682,12 @@
       <c r="G158" t="inlineStr"/>
       <c r="H158" s="6" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="7" t="n">
@@ -5930,7 +6721,12 @@
       </c>
       <c r="H159" s="7" t="inlineStr"/>
       <c r="I159" s="7" t="inlineStr"/>
-      <c r="J159" s="7" t="inlineStr"/>
+      <c r="J159" s="7" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K159" s="7" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -5960,7 +6756,12 @@
       <c r="G160" t="inlineStr"/>
       <c r="H160" s="6" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="n">
@@ -5994,7 +6795,12 @@
       </c>
       <c r="H161" s="7" t="inlineStr"/>
       <c r="I161" s="7" t="inlineStr"/>
-      <c r="J161" s="7" t="inlineStr"/>
+      <c r="J161" s="7" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K161" s="7" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -6024,7 +6830,12 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" s="6" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -6054,7 +6865,12 @@
       <c r="G163" t="inlineStr"/>
       <c r="H163" s="6" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -6084,7 +6900,12 @@
       <c r="G164" t="inlineStr"/>
       <c r="H164" s="6" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -6114,7 +6935,12 @@
       <c r="G165" t="inlineStr"/>
       <c r="H165" s="6" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -6144,7 +6970,12 @@
       <c r="G166" t="inlineStr"/>
       <c r="H166" s="6" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -6174,7 +7005,12 @@
       <c r="G167" t="inlineStr"/>
       <c r="H167" s="6" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -6204,7 +7040,12 @@
       <c r="G168" t="inlineStr"/>
       <c r="H168" s="6" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -6234,7 +7075,12 @@
       <c r="G169" t="inlineStr"/>
       <c r="H169" s="6" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -6264,7 +7110,12 @@
       <c r="G170" t="inlineStr"/>
       <c r="H170" s="6" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -6294,7 +7145,12 @@
       <c r="G171" t="inlineStr"/>
       <c r="H171" s="6" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -6324,7 +7180,12 @@
       <c r="G172" t="inlineStr"/>
       <c r="H172" s="6" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -6354,7 +7215,12 @@
       <c r="G173" t="inlineStr"/>
       <c r="H173" s="6" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -6384,7 +7250,12 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" s="6" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -6414,7 +7285,12 @@
       <c r="G175" t="inlineStr"/>
       <c r="H175" s="6" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -6444,7 +7320,12 @@
       <c r="G176" t="inlineStr"/>
       <c r="H176" s="6" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -6474,7 +7355,12 @@
       <c r="G177" t="inlineStr"/>
       <c r="H177" s="6" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="7" t="n">
@@ -6508,7 +7394,12 @@
       </c>
       <c r="H178" s="7" t="inlineStr"/>
       <c r="I178" s="7" t="inlineStr"/>
-      <c r="J178" s="7" t="inlineStr"/>
+      <c r="J178" s="7" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K178" s="7" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -6538,7 +7429,12 @@
       <c r="G179" t="inlineStr"/>
       <c r="H179" s="6" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -6568,7 +7464,12 @@
       <c r="G180" t="inlineStr"/>
       <c r="H180" s="6" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -6598,7 +7499,12 @@
       <c r="G181" t="inlineStr"/>
       <c r="H181" s="6" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -6628,7 +7534,12 @@
       <c r="G182" t="inlineStr"/>
       <c r="H182" s="6" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -6658,7 +7569,12 @@
       <c r="G183" t="inlineStr"/>
       <c r="H183" s="6" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -6688,7 +7604,12 @@
       <c r="G184" t="inlineStr"/>
       <c r="H184" s="6" t="inlineStr"/>
       <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -6718,7 +7639,12 @@
       <c r="G185" t="inlineStr"/>
       <c r="H185" s="6" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -6748,7 +7674,12 @@
       <c r="G186" t="inlineStr"/>
       <c r="H186" s="6" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -6778,7 +7709,12 @@
       <c r="G187" t="inlineStr"/>
       <c r="H187" s="6" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -6808,7 +7744,12 @@
       <c r="G188" t="inlineStr"/>
       <c r="H188" s="6" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -6838,7 +7779,12 @@
       <c r="G189" t="inlineStr"/>
       <c r="H189" s="6" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -6868,7 +7814,12 @@
       <c r="G190" t="inlineStr"/>
       <c r="H190" s="6" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -6898,7 +7849,12 @@
       <c r="G191" t="inlineStr"/>
       <c r="H191" s="6" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="7" t="n">
@@ -6932,7 +7888,12 @@
       </c>
       <c r="H192" s="7" t="inlineStr"/>
       <c r="I192" s="7" t="inlineStr"/>
-      <c r="J192" s="7" t="inlineStr"/>
+      <c r="J192" s="7" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K192" s="7" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -6962,7 +7923,12 @@
       <c r="G193" t="inlineStr"/>
       <c r="H193" s="6" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -6992,7 +7958,12 @@
       <c r="G194" t="inlineStr"/>
       <c r="H194" s="6" t="inlineStr"/>
       <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -7022,7 +7993,12 @@
       <c r="G195" t="inlineStr"/>
       <c r="H195" s="6" t="inlineStr"/>
       <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -7052,7 +8028,12 @@
       <c r="G196" t="inlineStr"/>
       <c r="H196" s="6" t="inlineStr"/>
       <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -7082,7 +8063,12 @@
       <c r="G197" t="inlineStr"/>
       <c r="H197" s="6" t="inlineStr"/>
       <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -7112,7 +8098,12 @@
       <c r="G198" t="inlineStr"/>
       <c r="H198" s="6" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -7142,7 +8133,12 @@
       <c r="G199" t="inlineStr"/>
       <c r="H199" s="6" t="inlineStr"/>
       <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -7172,7 +8168,12 @@
       <c r="G200" t="inlineStr"/>
       <c r="H200" s="6" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -7202,10 +8203,15 @@
       <c r="G201" t="inlineStr"/>
       <c r="H201" s="6" t="inlineStr"/>
       <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>(해당 없음)</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J201"/>
+  <autoFilter ref="A1:K201"/>
   <dataValidations count="1">
     <dataValidation sqref="H2:H201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A 누락·사전추가,B 누락·사전제외,C 경계·정의결정,D 아님,E 보류"</formula1>
@@ -7221,7 +8227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J201"/>
+  <dimension ref="A1:K201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7232,8 +8238,9 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7279,10 +8286,15 @@
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>추가할 표현(A일 때)</t>
+          <t>추가할 표현(A일 때, 문장에 나온 말 그대로)</t>
         </is>
       </c>
       <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>집계 대상(A일 때: 지역=시·도, 미디어=서브태그)</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -7317,6 +8329,7 @@
       <c r="H2" s="6" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -7347,6 +8360,7 @@
       <c r="H3" s="6" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -7377,6 +8391,7 @@
       <c r="H4" s="6" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -7407,6 +8422,7 @@
       <c r="H5" s="6" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -7437,6 +8453,7 @@
       <c r="H6" s="6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -7467,6 +8484,7 @@
       <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -7497,6 +8515,7 @@
       <c r="H8" s="6" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -7527,6 +8546,7 @@
       <c r="H9" s="6" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7557,6 +8577,7 @@
       <c r="H10" s="6" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7587,6 +8608,7 @@
       <c r="H11" s="6" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7617,6 +8639,7 @@
       <c r="H12" s="6" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7647,6 +8670,7 @@
       <c r="H13" s="6" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -7677,6 +8701,7 @@
       <c r="H14" s="6" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -7711,6 +8736,7 @@
       <c r="H15" s="7" t="inlineStr"/>
       <c r="I15" s="7" t="inlineStr"/>
       <c r="J15" s="7" t="inlineStr"/>
+      <c r="K15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -7741,6 +8767,7 @@
       <c r="H16" s="6" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -7771,6 +8798,7 @@
       <c r="H17" s="6" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -7801,6 +8829,7 @@
       <c r="H18" s="6" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -7831,6 +8860,7 @@
       <c r="H19" s="6" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -7861,6 +8891,7 @@
       <c r="H20" s="6" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -7899,6 +8930,7 @@
       <c r="H21" s="7" t="inlineStr"/>
       <c r="I21" s="7" t="inlineStr"/>
       <c r="J21" s="7" t="inlineStr"/>
+      <c r="K21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -7929,6 +8961,7 @@
       <c r="H22" s="6" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -7959,6 +8992,7 @@
       <c r="H23" s="6" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -7993,6 +9027,7 @@
       <c r="H24" s="7" t="inlineStr"/>
       <c r="I24" s="7" t="inlineStr"/>
       <c r="J24" s="7" t="inlineStr"/>
+      <c r="K24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -8027,6 +9062,7 @@
       <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr"/>
       <c r="J25" s="7" t="inlineStr"/>
+      <c r="K25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -8057,6 +9093,7 @@
       <c r="H26" s="6" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -8087,6 +9124,7 @@
       <c r="H27" s="6" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -8117,6 +9155,7 @@
       <c r="H28" s="6" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -8147,6 +9186,7 @@
       <c r="H29" s="6" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -8181,6 +9221,7 @@
       <c r="H30" s="7" t="inlineStr"/>
       <c r="I30" s="7" t="inlineStr"/>
       <c r="J30" s="7" t="inlineStr"/>
+      <c r="K30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -8211,6 +9252,7 @@
       <c r="H31" s="6" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -8241,6 +9283,7 @@
       <c r="H32" s="6" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -8271,6 +9314,7 @@
       <c r="H33" s="6" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -8301,6 +9345,7 @@
       <c r="H34" s="6" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -8331,6 +9376,7 @@
       <c r="H35" s="6" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -8365,6 +9411,7 @@
       <c r="H36" s="7" t="inlineStr"/>
       <c r="I36" s="7" t="inlineStr"/>
       <c r="J36" s="7" t="inlineStr"/>
+      <c r="K36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -8395,6 +9442,7 @@
       <c r="H37" s="6" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -8425,6 +9473,7 @@
       <c r="H38" s="6" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -8455,6 +9504,7 @@
       <c r="H39" s="6" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -8485,6 +9535,7 @@
       <c r="H40" s="6" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -8515,6 +9566,7 @@
       <c r="H41" s="6" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -8545,6 +9597,7 @@
       <c r="H42" s="6" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -8575,6 +9628,7 @@
       <c r="H43" s="6" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -8605,6 +9659,7 @@
       <c r="H44" s="6" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -8635,6 +9690,7 @@
       <c r="H45" s="6" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -8665,6 +9721,7 @@
       <c r="H46" s="6" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -8695,6 +9752,7 @@
       <c r="H47" s="6" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -8725,6 +9783,7 @@
       <c r="H48" s="6" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -8755,6 +9814,7 @@
       <c r="H49" s="6" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -8785,6 +9845,7 @@
       <c r="H50" s="6" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -8815,6 +9876,7 @@
       <c r="H51" s="6" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -8845,6 +9907,7 @@
       <c r="H52" s="6" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -8875,6 +9938,7 @@
       <c r="H53" s="6" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -8905,6 +9969,7 @@
       <c r="H54" s="6" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -8939,6 +10004,7 @@
       <c r="H55" s="7" t="inlineStr"/>
       <c r="I55" s="7" t="inlineStr"/>
       <c r="J55" s="7" t="inlineStr"/>
+      <c r="K55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8969,6 +10035,7 @@
       <c r="H56" s="6" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8999,6 +10066,7 @@
       <c r="H57" s="6" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -9029,6 +10097,7 @@
       <c r="H58" s="6" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -9059,6 +10128,7 @@
       <c r="H59" s="6" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -9089,6 +10159,7 @@
       <c r="H60" s="6" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -9119,6 +10190,7 @@
       <c r="H61" s="6" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -9149,6 +10221,7 @@
       <c r="H62" s="6" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -9179,6 +10252,7 @@
       <c r="H63" s="6" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -9209,6 +10283,7 @@
       <c r="H64" s="6" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -9239,6 +10314,7 @@
       <c r="H65" s="6" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -9269,6 +10345,7 @@
       <c r="H66" s="6" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -9299,6 +10376,7 @@
       <c r="H67" s="6" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9329,6 +10407,7 @@
       <c r="H68" s="6" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9359,6 +10438,7 @@
       <c r="H69" s="6" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9389,6 +10469,7 @@
       <c r="H70" s="6" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
@@ -9423,6 +10504,7 @@
       <c r="H71" s="7" t="inlineStr"/>
       <c r="I71" s="7" t="inlineStr"/>
       <c r="J71" s="7" t="inlineStr"/>
+      <c r="K71" s="7" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9453,6 +10535,7 @@
       <c r="H72" s="6" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9483,6 +10566,7 @@
       <c r="H73" s="6" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9513,6 +10597,7 @@
       <c r="H74" s="6" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9543,6 +10628,7 @@
       <c r="H75" s="6" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9573,6 +10659,7 @@
       <c r="H76" s="6" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9603,6 +10690,7 @@
       <c r="H77" s="6" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9633,6 +10721,7 @@
       <c r="H78" s="6" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9663,6 +10752,7 @@
       <c r="H79" s="6" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9693,6 +10783,7 @@
       <c r="H80" s="6" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9723,6 +10814,7 @@
       <c r="H81" s="6" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9753,6 +10845,7 @@
       <c r="H82" s="6" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9783,6 +10876,7 @@
       <c r="H83" s="6" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9813,6 +10907,7 @@
       <c r="H84" s="6" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9843,6 +10938,7 @@
       <c r="H85" s="6" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9873,6 +10969,7 @@
       <c r="H86" s="6" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9903,6 +11000,7 @@
       <c r="H87" s="6" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9933,6 +11031,7 @@
       <c r="H88" s="6" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9963,6 +11062,7 @@
       <c r="H89" s="6" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9993,6 +11093,7 @@
       <c r="H90" s="6" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10023,6 +11124,7 @@
       <c r="H91" s="6" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10053,6 +11155,7 @@
       <c r="H92" s="6" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10083,6 +11186,7 @@
       <c r="H93" s="6" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10113,6 +11217,7 @@
       <c r="H94" s="6" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10143,6 +11248,7 @@
       <c r="H95" s="6" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10173,6 +11279,7 @@
       <c r="H96" s="6" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10203,6 +11310,7 @@
       <c r="H97" s="6" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
@@ -10237,6 +11345,7 @@
       <c r="H98" s="7" t="inlineStr"/>
       <c r="I98" s="7" t="inlineStr"/>
       <c r="J98" s="7" t="inlineStr"/>
+      <c r="K98" s="7" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10267,6 +11376,7 @@
       <c r="H99" s="6" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10297,6 +11407,7 @@
       <c r="H100" s="6" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10327,6 +11438,7 @@
       <c r="H101" s="6" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10357,6 +11469,7 @@
       <c r="H102" s="6" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10387,6 +11500,7 @@
       <c r="H103" s="6" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10417,6 +11531,7 @@
       <c r="H104" s="6" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10447,6 +11562,7 @@
       <c r="H105" s="6" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10477,6 +11593,7 @@
       <c r="H106" s="6" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -10507,6 +11624,7 @@
       <c r="H107" s="6" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -10537,6 +11655,7 @@
       <c r="H108" s="6" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -10567,6 +11686,7 @@
       <c r="H109" s="6" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -10597,6 +11717,7 @@
       <c r="H110" s="6" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -10627,6 +11748,7 @@
       <c r="H111" s="6" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -10657,6 +11779,7 @@
       <c r="H112" s="6" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -10687,6 +11810,7 @@
       <c r="H113" s="6" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -10717,6 +11841,7 @@
       <c r="H114" s="6" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -10747,6 +11872,7 @@
       <c r="H115" s="6" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -10777,6 +11903,7 @@
       <c r="H116" s="6" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -10807,6 +11934,7 @@
       <c r="H117" s="6" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -10837,6 +11965,7 @@
       <c r="H118" s="6" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -10867,6 +11996,7 @@
       <c r="H119" s="6" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -10897,6 +12027,7 @@
       <c r="H120" s="6" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -10927,6 +12058,7 @@
       <c r="H121" s="6" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -10957,6 +12089,7 @@
       <c r="H122" s="6" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -10987,6 +12120,7 @@
       <c r="H123" s="6" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -11017,6 +12151,7 @@
       <c r="H124" s="6" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -11047,6 +12182,7 @@
       <c r="H125" s="6" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n">
@@ -11085,6 +12221,7 @@
       <c r="H126" s="7" t="inlineStr"/>
       <c r="I126" s="7" t="inlineStr"/>
       <c r="J126" s="7" t="inlineStr"/>
+      <c r="K126" s="7" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -11115,6 +12252,7 @@
       <c r="H127" s="6" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n">
@@ -11153,6 +12291,7 @@
       <c r="H128" s="7" t="inlineStr"/>
       <c r="I128" s="7" t="inlineStr"/>
       <c r="J128" s="7" t="inlineStr"/>
+      <c r="K128" s="7" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -11183,6 +12322,7 @@
       <c r="H129" s="6" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -11213,6 +12353,7 @@
       <c r="H130" s="6" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -11243,6 +12384,7 @@
       <c r="H131" s="6" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -11273,6 +12415,7 @@
       <c r="H132" s="6" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="7" t="n">
@@ -11307,6 +12450,7 @@
       <c r="H133" s="7" t="inlineStr"/>
       <c r="I133" s="7" t="inlineStr"/>
       <c r="J133" s="7" t="inlineStr"/>
+      <c r="K133" s="7" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -11337,6 +12481,7 @@
       <c r="H134" s="6" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -11367,6 +12512,7 @@
       <c r="H135" s="6" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -11397,6 +12543,7 @@
       <c r="H136" s="6" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -11427,6 +12574,7 @@
       <c r="H137" s="6" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -11457,6 +12605,7 @@
       <c r="H138" s="6" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -11487,6 +12636,7 @@
       <c r="H139" s="6" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -11517,6 +12667,7 @@
       <c r="H140" s="6" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -11547,6 +12698,7 @@
       <c r="H141" s="6" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -11577,6 +12729,7 @@
       <c r="H142" s="6" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -11607,6 +12760,7 @@
       <c r="H143" s="6" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -11637,6 +12791,7 @@
       <c r="H144" s="6" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -11667,6 +12822,7 @@
       <c r="H145" s="6" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n">
@@ -11701,6 +12857,7 @@
       <c r="H146" s="7" t="inlineStr"/>
       <c r="I146" s="7" t="inlineStr"/>
       <c r="J146" s="7" t="inlineStr"/>
+      <c r="K146" s="7" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -11731,6 +12888,7 @@
       <c r="H147" s="6" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -11761,6 +12919,7 @@
       <c r="H148" s="6" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -11791,6 +12950,7 @@
       <c r="H149" s="6" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="7" t="n">
@@ -11825,6 +12985,7 @@
       <c r="H150" s="7" t="inlineStr"/>
       <c r="I150" s="7" t="inlineStr"/>
       <c r="J150" s="7" t="inlineStr"/>
+      <c r="K150" s="7" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -11855,6 +13016,7 @@
       <c r="H151" s="6" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -11885,6 +13047,7 @@
       <c r="H152" s="6" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -11915,6 +13078,7 @@
       <c r="H153" s="6" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -11945,6 +13109,7 @@
       <c r="H154" s="6" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -11975,6 +13140,7 @@
       <c r="H155" s="6" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -12005,6 +13171,7 @@
       <c r="H156" s="6" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -12035,6 +13202,7 @@
       <c r="H157" s="6" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -12065,6 +13233,7 @@
       <c r="H158" s="6" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -12099,6 +13268,7 @@
       <c r="H159" s="6" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -12129,6 +13299,7 @@
       <c r="H160" s="6" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -12159,6 +13330,7 @@
       <c r="H161" s="6" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -12189,6 +13361,7 @@
       <c r="H162" s="6" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="7" t="n">
@@ -12223,6 +13396,7 @@
       <c r="H163" s="7" t="inlineStr"/>
       <c r="I163" s="7" t="inlineStr"/>
       <c r="J163" s="7" t="inlineStr"/>
+      <c r="K163" s="7" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -12253,6 +13427,7 @@
       <c r="H164" s="6" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -12283,6 +13458,7 @@
       <c r="H165" s="6" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -12313,6 +13489,7 @@
       <c r="H166" s="6" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -12343,6 +13520,7 @@
       <c r="H167" s="6" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -12373,6 +13551,7 @@
       <c r="H168" s="6" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -12403,6 +13582,7 @@
       <c r="H169" s="6" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -12433,6 +13613,7 @@
       <c r="H170" s="6" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -12463,6 +13644,7 @@
       <c r="H171" s="6" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -12493,6 +13675,7 @@
       <c r="H172" s="6" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -12523,6 +13706,7 @@
       <c r="H173" s="6" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -12553,6 +13737,7 @@
       <c r="H174" s="6" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -12583,6 +13768,7 @@
       <c r="H175" s="6" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -12613,6 +13799,7 @@
       <c r="H176" s="6" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -12643,6 +13830,7 @@
       <c r="H177" s="6" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -12673,6 +13861,7 @@
       <c r="H178" s="6" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -12703,6 +13892,7 @@
       <c r="H179" s="6" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -12733,6 +13923,7 @@
       <c r="H180" s="6" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -12763,6 +13954,7 @@
       <c r="H181" s="6" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -12793,6 +13985,7 @@
       <c r="H182" s="6" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -12823,6 +14016,7 @@
       <c r="H183" s="6" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -12853,6 +14047,7 @@
       <c r="H184" s="6" t="inlineStr"/>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -12883,6 +14078,7 @@
       <c r="H185" s="6" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -12913,6 +14109,7 @@
       <c r="H186" s="6" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -12943,6 +14140,7 @@
       <c r="H187" s="6" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -12973,6 +14171,7 @@
       <c r="H188" s="6" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -13003,6 +14202,7 @@
       <c r="H189" s="6" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -13033,6 +14233,7 @@
       <c r="H190" s="6" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="7" t="n">
@@ -13067,6 +14268,7 @@
       <c r="H191" s="7" t="inlineStr"/>
       <c r="I191" s="7" t="inlineStr"/>
       <c r="J191" s="7" t="inlineStr"/>
+      <c r="K191" s="7" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -13097,6 +14299,7 @@
       <c r="H192" s="6" t="inlineStr"/>
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -13127,6 +14330,7 @@
       <c r="H193" s="6" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -13157,6 +14361,7 @@
       <c r="H194" s="6" t="inlineStr"/>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -13187,6 +14392,7 @@
       <c r="H195" s="6" t="inlineStr"/>
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="7" t="n">
@@ -13221,6 +14427,7 @@
       <c r="H196" s="7" t="inlineStr"/>
       <c r="I196" s="7" t="inlineStr"/>
       <c r="J196" s="7" t="inlineStr"/>
+      <c r="K196" s="7" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -13251,6 +14458,7 @@
       <c r="H197" s="6" t="inlineStr"/>
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -13281,6 +14489,7 @@
       <c r="H198" s="6" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -13311,6 +14520,7 @@
       <c r="H199" s="6" t="inlineStr"/>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -13341,6 +14551,7 @@
       <c r="H200" s="6" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -13371,12 +14582,16 @@
       <c r="H201" s="6" t="inlineStr"/>
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J201"/>
-  <dataValidations count="1">
+  <autoFilter ref="A1:K201"/>
+  <dataValidations count="2">
     <dataValidation sqref="H2:H201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A 누락·사전추가,B 누락·사전제외,C 경계·정의결정,D 아님,E 보류"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"예능,유튜브,영화,드라마,라디오(신설·Q5),OTT·웹(신설·Q8),기타(메모에 적기)"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13389,7 +14604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J201"/>
+  <dimension ref="A1:K201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -13400,8 +14615,9 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13447,10 +14663,15 @@
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>추가할 표현(A일 때)</t>
+          <t>추가할 표현(A일 때, 문장에 나온 말 그대로)</t>
         </is>
       </c>
       <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>집계 대상(A일 때: 지역=시·도, 미디어=서브태그)</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -13485,6 +14706,7 @@
       <c r="H2" s="6" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -13515,6 +14737,7 @@
       <c r="H3" s="6" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -13545,6 +14768,7 @@
       <c r="H4" s="6" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -13575,6 +14799,7 @@
       <c r="H5" s="6" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -13605,6 +14830,7 @@
       <c r="H6" s="6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -13635,6 +14861,7 @@
       <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -13665,6 +14892,7 @@
       <c r="H8" s="6" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -13695,6 +14923,7 @@
       <c r="H9" s="6" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -13725,6 +14954,7 @@
       <c r="H10" s="6" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -13755,6 +14985,7 @@
       <c r="H11" s="6" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -13785,6 +15016,7 @@
       <c r="H12" s="6" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -13815,6 +15047,7 @@
       <c r="H13" s="6" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -13845,6 +15078,7 @@
       <c r="H14" s="6" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -13875,6 +15109,7 @@
       <c r="H15" s="6" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -13905,6 +15140,7 @@
       <c r="H16" s="6" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -13935,6 +15171,7 @@
       <c r="H17" s="6" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -13965,6 +15202,7 @@
       <c r="H18" s="6" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -13995,6 +15233,7 @@
       <c r="H19" s="6" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -14025,6 +15264,7 @@
       <c r="H20" s="6" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -14055,6 +15295,7 @@
       <c r="H21" s="6" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -14085,6 +15326,7 @@
       <c r="H22" s="6" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -14115,6 +15357,7 @@
       <c r="H23" s="6" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -14145,6 +15388,7 @@
       <c r="H24" s="6" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -14175,6 +15419,7 @@
       <c r="H25" s="6" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -14205,6 +15450,7 @@
       <c r="H26" s="6" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -14235,6 +15481,7 @@
       <c r="H27" s="6" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -14265,6 +15512,7 @@
       <c r="H28" s="6" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -14295,6 +15543,7 @@
       <c r="H29" s="6" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -14325,6 +15574,7 @@
       <c r="H30" s="6" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -14355,6 +15605,7 @@
       <c r="H31" s="6" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -14385,6 +15636,7 @@
       <c r="H32" s="6" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -14415,6 +15667,7 @@
       <c r="H33" s="6" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -14445,6 +15698,7 @@
       <c r="H34" s="6" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -14475,6 +15729,7 @@
       <c r="H35" s="6" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -14505,6 +15760,7 @@
       <c r="H36" s="6" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -14535,6 +15791,7 @@
       <c r="H37" s="6" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -14565,6 +15822,7 @@
       <c r="H38" s="6" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -14595,6 +15853,7 @@
       <c r="H39" s="6" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -14625,6 +15884,7 @@
       <c r="H40" s="6" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -14655,6 +15915,7 @@
       <c r="H41" s="6" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -14685,6 +15946,7 @@
       <c r="H42" s="6" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -14715,6 +15977,7 @@
       <c r="H43" s="6" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -14749,6 +16012,7 @@
       <c r="H44" s="7" t="inlineStr"/>
       <c r="I44" s="7" t="inlineStr"/>
       <c r="J44" s="7" t="inlineStr"/>
+      <c r="K44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -14779,6 +16043,7 @@
       <c r="H45" s="6" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -14809,6 +16074,7 @@
       <c r="H46" s="6" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -14839,6 +16105,7 @@
       <c r="H47" s="6" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -14869,6 +16136,7 @@
       <c r="H48" s="6" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -14899,6 +16167,7 @@
       <c r="H49" s="6" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -14929,6 +16198,7 @@
       <c r="H50" s="6" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -14959,6 +16229,7 @@
       <c r="H51" s="6" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -14993,6 +16264,7 @@
       <c r="H52" s="7" t="inlineStr"/>
       <c r="I52" s="7" t="inlineStr"/>
       <c r="J52" s="7" t="inlineStr"/>
+      <c r="K52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -15023,6 +16295,7 @@
       <c r="H53" s="6" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -15053,6 +16326,7 @@
       <c r="H54" s="6" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -15083,6 +16357,7 @@
       <c r="H55" s="6" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -15113,6 +16388,7 @@
       <c r="H56" s="6" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -15143,6 +16419,7 @@
       <c r="H57" s="6" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -15173,6 +16450,7 @@
       <c r="H58" s="6" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -15203,6 +16481,7 @@
       <c r="H59" s="6" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -15233,6 +16512,7 @@
       <c r="H60" s="6" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -15263,6 +16543,7 @@
       <c r="H61" s="6" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -15293,6 +16574,7 @@
       <c r="H62" s="6" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -15323,6 +16605,7 @@
       <c r="H63" s="6" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -15353,6 +16636,7 @@
       <c r="H64" s="6" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -15383,6 +16667,7 @@
       <c r="H65" s="6" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -15413,6 +16698,7 @@
       <c r="H66" s="6" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -15443,6 +16729,7 @@
       <c r="H67" s="6" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -15473,6 +16760,7 @@
       <c r="H68" s="6" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -15503,6 +16791,7 @@
       <c r="H69" s="6" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -15537,6 +16826,7 @@
       <c r="H70" s="7" t="inlineStr"/>
       <c r="I70" s="7" t="inlineStr"/>
       <c r="J70" s="7" t="inlineStr"/>
+      <c r="K70" s="7" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -15567,6 +16857,7 @@
       <c r="H71" s="6" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -15597,6 +16888,7 @@
       <c r="H72" s="6" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -15627,6 +16919,7 @@
       <c r="H73" s="6" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -15657,6 +16950,7 @@
       <c r="H74" s="6" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -15687,6 +16981,7 @@
       <c r="H75" s="6" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -15717,6 +17012,7 @@
       <c r="H76" s="6" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -15747,6 +17043,7 @@
       <c r="H77" s="6" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -15777,6 +17074,7 @@
       <c r="H78" s="6" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -15807,6 +17105,7 @@
       <c r="H79" s="6" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -15837,6 +17136,7 @@
       <c r="H80" s="6" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -15867,6 +17167,7 @@
       <c r="H81" s="6" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -15897,6 +17198,7 @@
       <c r="H82" s="6" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -15927,6 +17229,7 @@
       <c r="H83" s="6" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -15957,6 +17260,7 @@
       <c r="H84" s="6" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -15987,6 +17291,7 @@
       <c r="H85" s="6" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -16017,6 +17322,7 @@
       <c r="H86" s="6" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -16047,6 +17353,7 @@
       <c r="H87" s="6" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -16077,6 +17384,7 @@
       <c r="H88" s="6" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -16107,6 +17415,7 @@
       <c r="H89" s="6" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -16137,6 +17446,7 @@
       <c r="H90" s="6" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -16167,6 +17477,7 @@
       <c r="H91" s="6" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -16197,6 +17508,7 @@
       <c r="H92" s="6" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -16227,6 +17539,7 @@
       <c r="H93" s="6" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -16257,6 +17570,7 @@
       <c r="H94" s="6" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -16287,6 +17601,7 @@
       <c r="H95" s="6" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -16317,6 +17632,7 @@
       <c r="H96" s="6" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -16347,6 +17663,7 @@
       <c r="H97" s="6" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -16377,6 +17694,7 @@
       <c r="H98" s="6" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -16407,6 +17725,7 @@
       <c r="H99" s="6" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -16437,6 +17756,7 @@
       <c r="H100" s="6" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -16467,6 +17787,7 @@
       <c r="H101" s="6" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -16497,6 +17818,7 @@
       <c r="H102" s="6" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -16527,6 +17849,7 @@
       <c r="H103" s="6" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -16557,6 +17880,7 @@
       <c r="H104" s="6" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -16587,6 +17911,7 @@
       <c r="H105" s="6" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -16617,6 +17942,7 @@
       <c r="H106" s="6" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -16647,6 +17973,7 @@
       <c r="H107" s="6" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -16677,6 +18004,7 @@
       <c r="H108" s="6" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -16707,6 +18035,7 @@
       <c r="H109" s="6" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -16737,6 +18066,7 @@
       <c r="H110" s="6" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -16767,6 +18097,7 @@
       <c r="H111" s="6" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -16797,6 +18128,7 @@
       <c r="H112" s="6" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -16827,6 +18159,7 @@
       <c r="H113" s="6" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -16857,6 +18190,7 @@
       <c r="H114" s="6" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -16887,6 +18221,7 @@
       <c r="H115" s="6" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -16917,6 +18252,7 @@
       <c r="H116" s="6" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -16947,6 +18283,7 @@
       <c r="H117" s="6" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -16977,6 +18314,7 @@
       <c r="H118" s="6" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -17007,6 +18345,7 @@
       <c r="H119" s="6" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -17037,6 +18376,7 @@
       <c r="H120" s="6" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -17067,6 +18407,7 @@
       <c r="H121" s="6" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -17097,6 +18438,7 @@
       <c r="H122" s="6" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -17127,6 +18469,7 @@
       <c r="H123" s="6" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -17157,6 +18500,7 @@
       <c r="H124" s="6" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -17187,6 +18531,7 @@
       <c r="H125" s="6" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -17217,6 +18562,7 @@
       <c r="H126" s="6" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -17247,6 +18593,7 @@
       <c r="H127" s="6" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -17277,6 +18624,7 @@
       <c r="H128" s="6" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -17307,6 +18655,7 @@
       <c r="H129" s="6" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -17337,6 +18686,7 @@
       <c r="H130" s="6" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -17367,6 +18717,7 @@
       <c r="H131" s="6" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -17397,6 +18748,7 @@
       <c r="H132" s="6" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -17427,6 +18779,7 @@
       <c r="H133" s="6" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -17457,6 +18810,7 @@
       <c r="H134" s="6" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -17487,6 +18841,7 @@
       <c r="H135" s="6" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -17517,6 +18872,7 @@
       <c r="H136" s="6" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -17547,6 +18903,7 @@
       <c r="H137" s="6" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -17577,6 +18934,7 @@
       <c r="H138" s="6" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -17607,6 +18965,7 @@
       <c r="H139" s="6" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -17637,6 +18996,7 @@
       <c r="H140" s="6" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -17667,6 +19027,7 @@
       <c r="H141" s="6" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -17697,6 +19058,7 @@
       <c r="H142" s="6" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -17727,6 +19089,7 @@
       <c r="H143" s="6" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -17757,6 +19120,7 @@
       <c r="H144" s="6" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -17787,6 +19151,7 @@
       <c r="H145" s="6" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -17817,6 +19182,7 @@
       <c r="H146" s="6" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17847,6 +19213,7 @@
       <c r="H147" s="6" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17877,6 +19244,7 @@
       <c r="H148" s="6" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17907,6 +19275,7 @@
       <c r="H149" s="6" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="7" t="n">
@@ -17941,6 +19310,7 @@
       <c r="H150" s="7" t="inlineStr"/>
       <c r="I150" s="7" t="inlineStr"/>
       <c r="J150" s="7" t="inlineStr"/>
+      <c r="K150" s="7" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="7" t="n">
@@ -17975,6 +19345,7 @@
       <c r="H151" s="7" t="inlineStr"/>
       <c r="I151" s="7" t="inlineStr"/>
       <c r="J151" s="7" t="inlineStr"/>
+      <c r="K151" s="7" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -18005,6 +19376,7 @@
       <c r="H152" s="6" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -18035,6 +19407,7 @@
       <c r="H153" s="6" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -18065,6 +19438,7 @@
       <c r="H154" s="6" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -18095,6 +19469,7 @@
       <c r="H155" s="6" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18125,6 +19500,7 @@
       <c r="H156" s="6" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18155,6 +19531,7 @@
       <c r="H157" s="6" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18185,6 +19562,7 @@
       <c r="H158" s="6" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18215,6 +19593,7 @@
       <c r="H159" s="6" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18245,6 +19624,7 @@
       <c r="H160" s="6" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18275,6 +19655,7 @@
       <c r="H161" s="6" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18305,6 +19686,7 @@
       <c r="H162" s="6" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18335,6 +19717,7 @@
       <c r="H163" s="6" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18365,6 +19748,7 @@
       <c r="H164" s="6" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18395,6 +19779,7 @@
       <c r="H165" s="6" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18425,6 +19810,7 @@
       <c r="H166" s="6" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="7" t="n">
@@ -18459,6 +19845,7 @@
       <c r="H167" s="7" t="inlineStr"/>
       <c r="I167" s="7" t="inlineStr"/>
       <c r="J167" s="7" t="inlineStr"/>
+      <c r="K167" s="7" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18489,6 +19876,7 @@
       <c r="H168" s="6" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18519,6 +19907,7 @@
       <c r="H169" s="6" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18549,6 +19938,7 @@
       <c r="H170" s="6" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18579,6 +19969,7 @@
       <c r="H171" s="6" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18609,6 +20000,7 @@
       <c r="H172" s="6" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18639,6 +20031,7 @@
       <c r="H173" s="6" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18669,6 +20062,7 @@
       <c r="H174" s="6" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18699,6 +20093,7 @@
       <c r="H175" s="6" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18729,6 +20124,7 @@
       <c r="H176" s="6" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18759,6 +20155,7 @@
       <c r="H177" s="6" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18789,6 +20186,7 @@
       <c r="H178" s="6" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18819,6 +20217,7 @@
       <c r="H179" s="6" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18849,6 +20248,7 @@
       <c r="H180" s="6" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18879,6 +20279,7 @@
       <c r="H181" s="6" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18909,6 +20310,7 @@
       <c r="H182" s="6" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18939,6 +20341,7 @@
       <c r="H183" s="6" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -18969,6 +20372,7 @@
       <c r="H184" s="6" t="inlineStr"/>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -18999,6 +20403,7 @@
       <c r="H185" s="6" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19029,6 +20434,7 @@
       <c r="H186" s="6" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19059,6 +20465,7 @@
       <c r="H187" s="6" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19089,6 +20496,7 @@
       <c r="H188" s="6" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19119,6 +20527,7 @@
       <c r="H189" s="6" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19149,6 +20558,7 @@
       <c r="H190" s="6" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19179,6 +20589,7 @@
       <c r="H191" s="6" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19209,6 +20620,7 @@
       <c r="H192" s="6" t="inlineStr"/>
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19239,6 +20651,7 @@
       <c r="H193" s="6" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -19269,6 +20682,7 @@
       <c r="H194" s="6" t="inlineStr"/>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -19299,6 +20713,7 @@
       <c r="H195" s="6" t="inlineStr"/>
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -19329,6 +20744,7 @@
       <c r="H196" s="6" t="inlineStr"/>
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -19359,6 +20775,7 @@
       <c r="H197" s="6" t="inlineStr"/>
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -19389,6 +20806,7 @@
       <c r="H198" s="6" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -19419,6 +20837,7 @@
       <c r="H199" s="6" t="inlineStr"/>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -19449,6 +20868,7 @@
       <c r="H200" s="6" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -19479,12 +20899,16 @@
       <c r="H201" s="6" t="inlineStr"/>
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J201"/>
-  <dataValidations count="1">
+  <autoFilter ref="A1:K201"/>
+  <dataValidations count="2">
     <dataValidation sqref="H2:H201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A 누락·사전추가,B 누락·사전제외,C 경계·정의결정,D 아님,E 보류"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"서울,부산,대구,인천,광주,대전,울산,세종,경기,강원,충북,충남,전북,전남,경북,경남,제주"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
